--- a/Vlad/export/Приложение_А.xlsx
+++ b/Vlad/export/Приложение_А.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD15"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -487,6 +487,10 @@
     <col width="14" customWidth="1" min="54" max="54"/>
     <col width="14" customWidth="1" min="55" max="55"/>
     <col width="14" customWidth="1" min="56" max="56"/>
+    <col width="14" customWidth="1" min="57" max="57"/>
+    <col width="14" customWidth="1" min="58" max="58"/>
+    <col width="14" customWidth="1" min="59" max="59"/>
+    <col width="14" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -757,15 +761,35 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>Mw1</t>
+          <t>Mw1вт</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Mc2cp</t>
+          <t>Mc2вт</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Mw1ср</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Mc2ср</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Mw1п</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Mc2п</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>d'2</t>
         </is>
@@ -932,12 +956,24 @@
         <v>273.4</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>0.731</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8017</v>
       </c>
       <c r="BD2" s="2" t="n">
+        <v>0.7309</v>
+      </c>
+      <c r="BE2" s="2" t="n">
+        <v>0.6903</v>
+      </c>
+      <c r="BF2" s="2" t="n">
+        <v>0.6708</v>
+      </c>
+      <c r="BG2" s="2" t="n">
+        <v>0.6415</v>
+      </c>
+      <c r="BH2" s="2" t="n">
         <v>0.5531</v>
       </c>
     </row>
@@ -1102,12 +1138,24 @@
         <v>302.7</v>
       </c>
       <c r="BB3" s="2" t="n">
+        <v>0.7979000000000001</v>
+      </c>
+      <c r="BC3" s="2" t="n">
+        <v>0.7544999999999999</v>
+      </c>
+      <c r="BD3" s="2" t="n">
         <v>0.706</v>
       </c>
-      <c r="BC3" s="2" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="BD3" s="2" t="n">
+      <c r="BE3" s="2" t="n">
+        <v>0.6692</v>
+      </c>
+      <c r="BF3" s="2" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="BG3" s="2" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="BH3" s="2" t="n">
         <v>0.6474</v>
       </c>
     </row>
@@ -1272,12 +1320,24 @@
         <v>334.3</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.753</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>0.651</v>
+        <v>0.7157</v>
       </c>
       <c r="BD4" s="2" t="n">
+        <v>0.6839</v>
+      </c>
+      <c r="BE4" s="2" t="n">
+        <v>0.6509</v>
+      </c>
+      <c r="BF4" s="2" t="n">
+        <v>0.6479</v>
+      </c>
+      <c r="BG4" s="2" t="n">
+        <v>0.6217</v>
+      </c>
+      <c r="BH4" s="2" t="n">
         <v>0.7192</v>
       </c>
     </row>
@@ -1442,12 +1502,24 @@
         <v>367.8</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>0.655</v>
+        <v>0.7073</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.627</v>
+        <v>0.6758</v>
       </c>
       <c r="BD5" s="2" t="n">
+        <v>0.6553</v>
+      </c>
+      <c r="BE5" s="2" t="n">
+        <v>0.6267</v>
+      </c>
+      <c r="BF5" s="2" t="n">
+        <v>0.6263</v>
+      </c>
+      <c r="BG5" s="2" t="n">
+        <v>0.6024</v>
+      </c>
+      <c r="BH5" s="2" t="n">
         <v>0.7714</v>
       </c>
     </row>
@@ -1612,12 +1684,24 @@
         <v>401.5</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>0.629</v>
+        <v>0.67</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.604</v>
+        <v>0.6427</v>
       </c>
       <c r="BD6" s="2" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="BE6" s="2" t="n">
+        <v>0.6042</v>
+      </c>
+      <c r="BF6" s="2" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="BG6" s="2" t="n">
+        <v>0.5836</v>
+      </c>
+      <c r="BH6" s="2" t="n">
         <v>0.8095</v>
       </c>
     </row>
@@ -1782,12 +1866,24 @@
         <v>435.3</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.606</v>
+        <v>0.6387</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.583</v>
+        <v>0.6143</v>
       </c>
       <c r="BD7" s="2" t="n">
+        <v>0.6062</v>
+      </c>
+      <c r="BE7" s="2" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="BF7" s="2" t="n">
+        <v>0.5863</v>
+      </c>
+      <c r="BG7" s="2" t="n">
+        <v>0.5659</v>
+      </c>
+      <c r="BH7" s="2" t="n">
         <v>0.8384</v>
       </c>
     </row>
@@ -1952,12 +2048,24 @@
         <v>469.2</v>
       </c>
       <c r="BB8" s="2" t="n">
-        <v>0.585</v>
+        <v>0.6116</v>
       </c>
       <c r="BC8" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5896</v>
       </c>
       <c r="BD8" s="2" t="n">
+        <v>0.5851</v>
+      </c>
+      <c r="BE8" s="2" t="n">
+        <v>0.5644</v>
+      </c>
+      <c r="BF8" s="2" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="BG8" s="2" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="BH8" s="2" t="n">
         <v>0.8608</v>
       </c>
     </row>
@@ -2122,12 +2230,24 @@
         <v>503</v>
       </c>
       <c r="BB9" s="2" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="BC9" s="2" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="BD9" s="2" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="BC9" s="2" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="BD9" s="2" t="n">
+      <c r="BE9" s="2" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="BF9" s="2" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="BG9" s="2" t="n">
+        <v>0.5336</v>
+      </c>
+      <c r="BH9" s="2" t="n">
         <v>0.8786</v>
       </c>
     </row>
@@ -2292,12 +2412,24 @@
         <v>536.7</v>
       </c>
       <c r="BB10" s="2" t="n">
-        <v>0.549</v>
+        <v>0.5671</v>
       </c>
       <c r="BC10" s="2" t="n">
-        <v>0.531</v>
+        <v>0.5484</v>
       </c>
       <c r="BD10" s="2" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="BE10" s="2" t="n">
+        <v>0.5306999999999999</v>
+      </c>
+      <c r="BF10" s="2" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="BG10" s="2" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="BH10" s="2" t="n">
         <v>0.893</v>
       </c>
     </row>
@@ -2462,12 +2594,24 @@
         <v>570.3</v>
       </c>
       <c r="BB11" s="2" t="n">
-        <v>0.533</v>
+        <v>0.5484</v>
       </c>
       <c r="BC11" s="2" t="n">
-        <v>0.516</v>
+        <v>0.5309</v>
       </c>
       <c r="BD11" s="2" t="n">
+        <v>0.5326</v>
+      </c>
+      <c r="BE11" s="2" t="n">
+        <v>0.5158</v>
+      </c>
+      <c r="BF11" s="2" t="n">
+        <v>0.5216</v>
+      </c>
+      <c r="BG11" s="2" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="BH11" s="2" t="n">
         <v>0.9048</v>
       </c>
     </row>
@@ -2632,12 +2776,24 @@
         <v>603.7</v>
       </c>
       <c r="BB12" s="2" t="n">
-        <v>0.518</v>
+        <v>0.5316</v>
       </c>
       <c r="BC12" s="2" t="n">
+        <v>0.5151</v>
+      </c>
+      <c r="BD12" s="2" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="BE12" s="2" t="n">
         <v>0.502</v>
       </c>
-      <c r="BD12" s="2" t="n">
+      <c r="BF12" s="2" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="BG12" s="2" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="BH12" s="2" t="n">
         <v>0.9147</v>
       </c>
     </row>
@@ -2802,12 +2958,24 @@
         <v>637</v>
       </c>
       <c r="BB13" s="2" t="n">
-        <v>0.504</v>
+        <v>0.5131</v>
       </c>
       <c r="BC13" s="2" t="n">
-        <v>0.489</v>
+        <v>0.4983</v>
       </c>
       <c r="BD13" s="2" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="BE13" s="2" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="BF13" s="2" t="n">
+        <v>0.4924</v>
+      </c>
+      <c r="BG13" s="2" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="BH13" s="2" t="n">
         <v>0.9224</v>
       </c>
     </row>
@@ -2972,12 +3140,24 @@
         <v>670.6</v>
       </c>
       <c r="BB14" s="2" t="n">
-        <v>0.494</v>
+        <v>0.5016</v>
       </c>
       <c r="BC14" s="2" t="n">
-        <v>0.458</v>
+        <v>0.467</v>
       </c>
       <c r="BD14" s="2" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="BE14" s="2" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="BF14" s="2" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="BG14" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BH14" s="2" t="n">
         <v>0.9282</v>
       </c>
     </row>
@@ -3142,12 +3322,24 @@
         <v>702.6</v>
       </c>
       <c r="BB15" s="2" t="n">
-        <v>0.492</v>
+        <v>0.4975</v>
       </c>
       <c r="BC15" s="2" t="n">
-        <v>0.424</v>
+        <v>0.4334</v>
       </c>
       <c r="BD15" s="2" t="n">
+        <v>0.4917</v>
+      </c>
+      <c r="BE15" s="2" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="BF15" s="2" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="BG15" s="2" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="BH15" s="2" t="n">
         <v>0.9313</v>
       </c>
     </row>

--- a/Vlad/export/Приложение_А.xlsx
+++ b/Vlad/export/Приложение_А.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -800,28 +800,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.6342</v>
+        <v>0.6998</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.4011</v>
+        <v>0.5394</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.45</v>
+        <v>0.5968</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>152.2</v>
+        <v>208.8</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8575</v>
+        <v>0.8335</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.2571</v>
+        <v>0.2026</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0.99</v>
@@ -830,151 +830,151 @@
         <v>0.5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>62.661</v>
+        <v>63.195</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>29403.187</v>
+        <v>24788.599</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>29109.155</v>
+        <v>24540.713</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>24961.89</v>
+        <v>20454.314</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>316.9</v>
+        <v>312.4</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>100.713</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>134.501</v>
+        <v>127.876</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>1.3355</v>
+        <v>1.2697</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>310.726</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>1.068</v>
+        <v>0.95</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.7906</v>
+        <v>0.8434</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.2327</v>
+        <v>0.3015</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.5513</v>
+        <v>0.7527</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.3826</v>
+        <v>0.3138</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.5134</v>
+        <v>0.7073</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.3224</v>
+        <v>0.2678</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.6018</v>
+        <v>0.7106</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.8253</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.2429</v>
+        <v>0.2947</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>60.875</v>
+        <v>62.357</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.4369</v>
+        <v>0.5633</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>147.7</v>
+        <v>197</v>
       </c>
       <c r="AJ2" s="2" t="n">
         <v>6</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>1.32</v>
+        <v>1.146</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.8079</v>
+        <v>0.8554</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>0.4323</v>
+        <v>0.5797</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5342</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>38.371</v>
+        <v>47.339</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>38.889</v>
+        <v>47.767</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>58.78</v>
+        <v>61.008</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>19.891</v>
+        <v>13.242</v>
       </c>
       <c r="AS2" s="2" t="n">
-        <v>22.504</v>
+        <v>15.018</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>146.2</v>
+        <v>202.8</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>171.303</v>
+        <v>233.882</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>235.468</v>
+        <v>275.711</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>242.379</v>
+        <v>281.939</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>170.921</v>
+        <v>231.798</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>316.9</v>
+        <v>312.4</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>273.4</v>
+        <v>260.8</v>
       </c>
       <c r="BB2" s="2" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.9466</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.8017</v>
+        <v>0.9024</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>0.7309</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="BE2" s="2" t="n">
-        <v>0.6903</v>
+        <v>0.8297</v>
       </c>
       <c r="BF2" s="2" t="n">
-        <v>0.6708</v>
+        <v>0.8254</v>
       </c>
       <c r="BG2" s="2" t="n">
-        <v>0.6415</v>
+        <v>0.7916</v>
       </c>
       <c r="BH2" s="2" t="n">
-        <v>0.5531</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="3">
@@ -982,28 +982,28 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.6634</v>
+        <v>0.7179</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.4863</v>
+        <v>0.585</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4369</v>
+        <v>0.5633</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>147.7</v>
+        <v>197</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.866</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.2802</v>
+        <v>0.2411</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0.986</v>
@@ -1012,151 +1012,151 @@
         <v>0.5</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.6061</v>
+        <v>0.705</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>60.815</v>
+        <v>62.504</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>32038.89</v>
+        <v>29500.043</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>31595.274</v>
+        <v>29082.126</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>27362.865</v>
+        <v>24992.084</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>348.3</v>
+        <v>341.2</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>134.501</v>
+        <v>127.876</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>179.436</v>
+        <v>167.159</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>1.3341</v>
+        <v>1.3072</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>325.922</v>
+        <v>323.587</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1.316</v>
+        <v>1.161</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.8269</v>
+        <v>0.8651</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.244</v>
+        <v>0.2932</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.5192</v>
+        <v>0.6864</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.3198</v>
+        <v>0.2721</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.4803</v>
+        <v>0.6403</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.2706</v>
+        <v>0.2284</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.6816</v>
+        <v>0.76</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.8558</v>
+        <v>0.8882</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>0.2515</v>
+        <v>0.2903</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>59.528</v>
+        <v>61.741</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.4279</v>
+        <v>0.5405</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>144.7</v>
+        <v>189</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>6.308</v>
+        <v>6.333</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>1.625</v>
+        <v>1.428</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.8413</v>
+        <v>0.8767</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.4182</v>
+        <v>0.5452</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.5729</v>
+        <v>0.5644</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>36.131</v>
+        <v>44.008</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>36.852</v>
+        <v>44.566</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>57.303</v>
+        <v>60.203</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>20.451</v>
+        <v>15.637</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>23.397</v>
+        <v>17.732</v>
       </c>
       <c r="AT3" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>141.4</v>
+        <v>190.7</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>169.204</v>
+        <v>222.125</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>239.839</v>
+        <v>274.482</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>246.311</v>
+        <v>280.784</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>168.045</v>
+        <v>219.754</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>348.3</v>
+        <v>341.2</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>302.7</v>
+        <v>287.9</v>
       </c>
       <c r="BB3" s="2" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.8911</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.848</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>0.706</v>
+        <v>0.8253</v>
       </c>
       <c r="BE3" s="2" t="n">
-        <v>0.6692</v>
+        <v>0.7855</v>
       </c>
       <c r="BF3" s="2" t="n">
-        <v>0.6601</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="BG3" s="2" t="n">
-        <v>0.6324</v>
+        <v>0.7568</v>
       </c>
       <c r="BH3" s="2" t="n">
-        <v>0.6474</v>
+        <v>0.7317</v>
       </c>
     </row>
     <row r="4">
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.6888</v>
+        <v>0.7365</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.5525</v>
+        <v>0.6294</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.4279</v>
+        <v>0.5405</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>144.7</v>
+        <v>189</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.8741</v>
+        <v>0.8768</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.3019</v>
+        <v>0.2731</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0.982</v>
@@ -1194,151 +1194,151 @@
         <v>0.5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.6887</v>
+        <v>0.7585</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>59.358</v>
+        <v>61.794</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>34520.688</v>
+        <v>33411.571</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>33909.937</v>
+        <v>32799.026</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>29639.383</v>
+        <v>28759.178</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>381.8</v>
+        <v>373.7</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>179.436</v>
+        <v>167.159</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>238.443</v>
+        <v>221.538</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>1.3288</v>
+        <v>1.3253</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>341.601</v>
+        <v>338.154</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1.617</v>
+        <v>1.433</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.8586</v>
+        <v>0.8875</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.2535</v>
+        <v>0.2899</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.4923</v>
+        <v>0.6344</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2657</v>
+        <v>0.2297</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.4578</v>
+        <v>0.5928</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>0.2266</v>
+        <v>0.1923</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.7428</v>
+        <v>0.8027</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.8808</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.2672</v>
+        <v>0.2952</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>57.507</v>
+        <v>60.412</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.42</v>
+        <v>0.5205</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>6.615</v>
+        <v>6.667</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>1.988</v>
+        <v>1.773</v>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.8697</v>
+        <v>0.8971</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.4083</v>
+        <v>0.5214</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.5974</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>34.355</v>
+        <v>41.412</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>35.266</v>
+        <v>42.127</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>56.299</v>
+        <v>59.6</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>21.033</v>
+        <v>17.474</v>
       </c>
       <c r="AS4" s="2" t="n">
-        <v>23.153</v>
+        <v>19.001</v>
       </c>
       <c r="AT4" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>138.1</v>
+        <v>182.4</v>
       </c>
       <c r="AV4" s="2" t="n">
-        <v>168.175</v>
+        <v>214.518</v>
       </c>
       <c r="AW4" s="2" t="n">
-        <v>244.682</v>
+        <v>275.719</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>250.606</v>
+        <v>281.832</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>165.97</v>
+        <v>211.449</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>381.8</v>
+        <v>373.7</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>334.3</v>
+        <v>318.4</v>
       </c>
       <c r="BB4" s="2" t="n">
-        <v>0.753</v>
+        <v>0.8408</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>0.7157</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>0.6839</v>
+        <v>0.7879</v>
       </c>
       <c r="BE4" s="2" t="n">
-        <v>0.6509</v>
+        <v>0.7507</v>
       </c>
       <c r="BF4" s="2" t="n">
-        <v>0.6479</v>
+        <v>0.7597</v>
       </c>
       <c r="BG4" s="2" t="n">
-        <v>0.6217</v>
+        <v>0.7281</v>
       </c>
       <c r="BH4" s="2" t="n">
-        <v>0.7192</v>
+        <v>0.7805</v>
       </c>
     </row>
     <row r="5">
@@ -1346,28 +1346,28 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.709</v>
+        <v>0.7523</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.6014</v>
+        <v>0.6659</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.42</v>
+        <v>0.5205</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8809</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.3051</v>
+        <v>0.2868</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.978</v>
@@ -1376,151 +1376,151 @@
         <v>0.5</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.7496</v>
+        <v>0.8025</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>57.342</v>
+        <v>60.442</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>34889.672</v>
+        <v>35081.343</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>34138.202</v>
+        <v>34292.013</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>29753.014</v>
+        <v>30207.393</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>415.5</v>
+        <v>407.6</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>238.443</v>
+        <v>221.538</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>309.618</v>
+        <v>290.375</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>1.2985</v>
+        <v>1.3107</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>357.585</v>
+        <v>353.796</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>1.977</v>
+        <v>1.775</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.8837</v>
+        <v>0.9066</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.2692</v>
+        <v>0.2952</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.4718</v>
+        <v>0.5915</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2215</v>
+        <v>0.1925</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.4373</v>
+        <v>0.5515</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.1926</v>
+        <v>0.1633</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.8355</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9214</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.2787</v>
+        <v>0.2987</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>55.957</v>
+        <v>59.236</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.4128</v>
+        <v>0.5021</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>139.6</v>
+        <v>175.6</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>6.923</v>
+        <v>7</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>2.391</v>
+        <v>2.176</v>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.8917</v>
+        <v>0.914</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.3996</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.609</v>
+        <v>0.6065</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>33.27</v>
+        <v>39.527</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>34.354</v>
+        <v>40.404</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>54.715</v>
+        <v>58.431</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>20.36</v>
+        <v>18.027</v>
       </c>
       <c r="AS5" s="2" t="n">
-        <v>22.687</v>
+        <v>19.709</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>135.1</v>
+        <v>175</v>
       </c>
       <c r="AV5" s="2" t="n">
-        <v>168.707</v>
+        <v>209.278</v>
       </c>
       <c r="AW5" s="2" t="n">
-        <v>246.294</v>
+        <v>275.031</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>251.697</v>
+        <v>280.853</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>165.521</v>
+        <v>205.444</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>415.5</v>
+        <v>407.6</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>367.8</v>
+        <v>352.1</v>
       </c>
       <c r="BB5" s="2" t="n">
-        <v>0.7073</v>
+        <v>0.7884</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>0.6758</v>
+        <v>0.7534</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>0.6553</v>
+        <v>0.7472</v>
       </c>
       <c r="BE5" s="2" t="n">
-        <v>0.6267</v>
+        <v>0.714</v>
       </c>
       <c r="BF5" s="2" t="n">
-        <v>0.6263</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="BG5" s="2" t="n">
-        <v>0.6024</v>
+        <v>0.6952</v>
       </c>
       <c r="BH5" s="2" t="n">
-        <v>0.7714</v>
+        <v>0.8192</v>
       </c>
     </row>
     <row r="6">
@@ -1528,181 +1528,181 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.7241</v>
+        <v>0.7648</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.6364</v>
+        <v>0.6937</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.4128</v>
+        <v>0.5021</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>139.6</v>
+        <v>175.6</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.869</v>
+        <v>0.8829</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.308</v>
+        <v>0.2986</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.975</v>
+        <v>0.973</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.7932</v>
+        <v>0.8359</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>55.789</v>
+        <v>59.24</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>35217.081</v>
+        <v>36525.414</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>34323.108</v>
+        <v>35551.403</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>29825.704</v>
+        <v>31387.597</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>449.2</v>
+        <v>442.5</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>309.618</v>
+        <v>290.375</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>394.132</v>
+        <v>375.951</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>1.273</v>
+        <v>1.2947</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>372.886</v>
+        <v>369.348</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>2.376</v>
+        <v>2.174</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.9026</v>
+        <v>0.9216</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.2807</v>
+        <v>0.2988</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.4527</v>
+        <v>0.5533</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1874</v>
+        <v>0.1629</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.4185</v>
+        <v>0.5149</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.1658</v>
+        <v>0.1401</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.8198</v>
+        <v>0.8608</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.9143</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.2873</v>
+        <v>0.3009</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>54.705</v>
+        <v>58.163</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.406</v>
+        <v>0.4848</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>137.3</v>
+        <v>169.6</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>7.231</v>
+        <v>7.333</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>2.834</v>
+        <v>2.639</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.9084</v>
+        <v>0.9273</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.3914</v>
+        <v>0.4811</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.6179</v>
+        <v>0.619</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>32.355</v>
+        <v>37.857</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>33.576</v>
+        <v>38.875</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>53.412</v>
+        <v>57.344</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>19.836</v>
+        <v>18.469</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>22.35</v>
+        <v>20.306</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>132.4</v>
+        <v>168.3</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>168.802</v>
+        <v>204.359</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>247.333</v>
+        <v>274.199</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>252.411</v>
+        <v>279.8</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>164.849</v>
+        <v>199.87</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>449.2</v>
+        <v>442.5</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>401.5</v>
+        <v>387.1</v>
       </c>
       <c r="BB6" s="2" t="n">
-        <v>0.67</v>
+        <v>0.7432</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>0.6427</v>
+        <v>0.7121</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.7105</v>
       </c>
       <c r="BE6" s="2" t="n">
-        <v>0.6042</v>
+        <v>0.6808</v>
       </c>
       <c r="BF6" s="2" t="n">
-        <v>0.6057</v>
+        <v>0.6917</v>
       </c>
       <c r="BG6" s="2" t="n">
-        <v>0.5836</v>
+        <v>0.665</v>
       </c>
       <c r="BH6" s="2" t="n">
-        <v>0.8095</v>
+        <v>0.8488</v>
       </c>
     </row>
     <row r="7">
@@ -1710,181 +1710,181 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.7357</v>
+        <v>0.7746</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.6625</v>
+        <v>0.7151</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.406</v>
+        <v>0.4848</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>137.3</v>
+        <v>169.6</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8663</v>
+        <v>0.8832</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.3106</v>
+        <v>0.309</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.971</v>
+        <v>0.969</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.8258</v>
+        <v>0.8617</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>54.541</v>
+        <v>58.15</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>35514.442</v>
+        <v>37803.095</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>34476.328</v>
+        <v>36637.499</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>29867.417</v>
+        <v>32359.667</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>482.9</v>
+        <v>478.4</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>394.132</v>
+        <v>375.951</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>493.153</v>
+        <v>480.677</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>1.2512</v>
+        <v>1.2786</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>387.551</v>
+        <v>384.695</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>2.817</v>
+        <v>2.634</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.9171</v>
+        <v>0.9334</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.2892</v>
+        <v>0.3012</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.435</v>
+        <v>0.5189</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1608</v>
+        <v>0.1392</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.4011</v>
+        <v>0.482</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.1444</v>
+        <v>0.1213</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.8452</v>
+        <v>0.8807</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>0.9258</v>
+        <v>0.9422</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.2939</v>
+        <v>0.3022</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>53.661</v>
+        <v>57.166</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.3996</v>
+        <v>0.4684</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>135.1</v>
+        <v>163.8</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>7.538</v>
+        <v>7.667</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>3.319</v>
+        <v>3.166</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.9214</v>
+        <v>0.9378</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.3838</v>
+        <v>0.4629</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.6249</v>
+        <v>0.6293</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>31.555</v>
+        <v>36.339</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>32.891</v>
+        <v>37.482</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>52.304</v>
+        <v>56.313</v>
       </c>
       <c r="AR7" s="2" t="n">
-        <v>19.413</v>
+        <v>18.831</v>
       </c>
       <c r="AS7" s="2" t="n">
-        <v>22.106</v>
+        <v>20.827</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>129.8</v>
+        <v>161.9</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>168.569</v>
+        <v>199.628</v>
       </c>
       <c r="AW7" s="2" t="n">
-        <v>247.97</v>
+        <v>273.23</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>252.844</v>
+        <v>278.666</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>163.999</v>
+        <v>194.578</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>482.9</v>
+        <v>478.4</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>435.3</v>
+        <v>423.1</v>
       </c>
       <c r="BB7" s="2" t="n">
-        <v>0.6387</v>
+        <v>0.7039</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.6143</v>
+        <v>0.676</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>0.6062</v>
+        <v>0.6776</v>
       </c>
       <c r="BE7" s="2" t="n">
-        <v>0.5835</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="BF7" s="2" t="n">
-        <v>0.5863</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="BG7" s="2" t="n">
-        <v>0.5659</v>
+        <v>0.6372</v>
       </c>
       <c r="BH7" s="2" t="n">
-        <v>0.8384</v>
+        <v>0.8718</v>
       </c>
     </row>
     <row r="8">
@@ -1892,181 +1892,181 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.7449</v>
+        <v>0.7823</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.6826</v>
+        <v>0.7318</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.3996</v>
+        <v>0.4684</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>135.1</v>
+        <v>163.8</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8636</v>
+        <v>0.8822</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.313</v>
+        <v>0.3184</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.967</v>
+        <v>0.965</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.8509</v>
+        <v>0.8819</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>53.502</v>
+        <v>57.14</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>35788.231</v>
+        <v>38948.05</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>34604.466</v>
+        <v>37584.868</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>29883.937</v>
+        <v>33158.289</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>516.5</v>
+        <v>514.9</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>493.153</v>
+        <v>480.677</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>607.843</v>
+        <v>607.037</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>1.2326</v>
+        <v>1.2629</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>401.624</v>
+        <v>399.765</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>3.298</v>
+        <v>3.158</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.9284</v>
+        <v>0.9428</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.2957</v>
+        <v>0.3026</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.4185</v>
+        <v>0.4879</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1395</v>
+        <v>0.1202</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.3851</v>
+        <v>0.4523</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.1271</v>
+        <v>0.1062</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.8652</v>
+        <v>0.8965</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9496</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.299</v>
+        <v>0.3027</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>52.764</v>
+        <v>56.219</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.3934</v>
+        <v>0.4527</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>133</v>
+        <v>158.3</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>7.846</v>
+        <v>8</v>
       </c>
       <c r="AK8" s="2" t="n">
-        <v>3.845</v>
+        <v>3.759</v>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.9317</v>
+        <v>0.9462</v>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>0.3764</v>
+        <v>0.4455</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6379</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>30.835</v>
+        <v>34.931</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>32.273</v>
+        <v>36.189</v>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>51.333</v>
+        <v>55.317</v>
       </c>
       <c r="AR8" s="2" t="n">
-        <v>19.06</v>
+        <v>19.128</v>
       </c>
       <c r="AS8" s="2" t="n">
-        <v>21.929</v>
+        <v>21.288</v>
       </c>
       <c r="AT8" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU8" s="2" t="n">
-        <v>127.3</v>
+        <v>155.8</v>
       </c>
       <c r="AV8" s="2" t="n">
-        <v>168.094</v>
+        <v>195.035</v>
       </c>
       <c r="AW8" s="2" t="n">
-        <v>248.318</v>
+        <v>272.152</v>
       </c>
       <c r="AX8" s="2" t="n">
-        <v>253.069</v>
+        <v>277.465</v>
       </c>
       <c r="AY8" s="2" t="n">
-        <v>163.016</v>
+        <v>189.501</v>
       </c>
       <c r="AZ8" s="2" t="n">
-        <v>516.5</v>
+        <v>514.9</v>
       </c>
       <c r="BA8" s="2" t="n">
-        <v>469.2</v>
+        <v>459.9</v>
       </c>
       <c r="BB8" s="2" t="n">
-        <v>0.6116</v>
+        <v>0.6693</v>
       </c>
       <c r="BC8" s="2" t="n">
-        <v>0.5896</v>
+        <v>0.6441</v>
       </c>
       <c r="BD8" s="2" t="n">
-        <v>0.5851</v>
+        <v>0.6479</v>
       </c>
       <c r="BE8" s="2" t="n">
-        <v>0.5644</v>
+        <v>0.6234</v>
       </c>
       <c r="BF8" s="2" t="n">
-        <v>0.5683</v>
+        <v>0.6345</v>
       </c>
       <c r="BG8" s="2" t="n">
-        <v>0.5492</v>
+        <v>0.6118</v>
       </c>
       <c r="BH8" s="2" t="n">
-        <v>0.8608</v>
+        <v>0.8899</v>
       </c>
     </row>
     <row r="9">
@@ -2074,181 +2074,181 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.7522</v>
+        <v>0.7886</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.6985</v>
+        <v>0.7451</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.3934</v>
+        <v>0.4527</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>133</v>
+        <v>158.3</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.8608</v>
+        <v>0.88</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.3152</v>
+        <v>0.3268</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.963</v>
+        <v>0.961</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.8706</v>
+        <v>0.8979</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>52.611</v>
+        <v>56.185</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>36042.582</v>
+        <v>39981.989</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>34711.779</v>
+        <v>38416.028</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>29879.079</v>
+        <v>33806.466</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>607.843</v>
+        <v>607.037</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>739.353</v>
+        <v>757.544</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>1.2164</v>
+        <v>1.2479</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>415.15</v>
+        <v>414.517</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>3.821</v>
+        <v>3.748</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.9376</v>
+        <v>0.9503</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.3007</v>
+        <v>0.3032</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.4033</v>
+        <v>0.4597</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1223</v>
+        <v>0.1048</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.3703</v>
+        <v>0.4253</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>0.1129</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>0.8813</v>
+        <v>0.9091</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>0.9425</v>
+        <v>0.9557</v>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.3029</v>
+        <v>0.3028</v>
       </c>
       <c r="AG9" s="2" t="n">
-        <v>51.976</v>
+        <v>55.305</v>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0.3875</v>
+        <v>0.4375</v>
       </c>
       <c r="AI9" s="2" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="AJ9" s="2" t="n">
-        <v>8.154</v>
+        <v>8.333</v>
       </c>
       <c r="AK9" s="2" t="n">
-        <v>4.413</v>
+        <v>4.421</v>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.953</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>0.3693</v>
+        <v>0.4288</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>0.6352</v>
+        <v>0.6453</v>
       </c>
       <c r="AO9" s="2" t="n">
-        <v>30.175</v>
+        <v>33.606</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>31.705</v>
+        <v>34.973</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>50.462</v>
+        <v>54.341</v>
       </c>
       <c r="AR9" s="2" t="n">
-        <v>18.757</v>
+        <v>19.368</v>
       </c>
       <c r="AS9" s="2" t="n">
-        <v>21.801</v>
+        <v>21.699</v>
       </c>
       <c r="AT9" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU9" s="2" t="n">
-        <v>124.9</v>
+        <v>150</v>
       </c>
       <c r="AV9" s="2" t="n">
-        <v>167.443</v>
+        <v>190.56</v>
       </c>
       <c r="AW9" s="2" t="n">
-        <v>248.458</v>
+        <v>270.997</v>
       </c>
       <c r="AX9" s="2" t="n">
-        <v>253.139</v>
+        <v>276.215</v>
       </c>
       <c r="AY9" s="2" t="n">
-        <v>161.934</v>
+        <v>184.603</v>
       </c>
       <c r="AZ9" s="2" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="BA9" s="2" t="n">
-        <v>503</v>
+        <v>497.4</v>
       </c>
       <c r="BB9" s="2" t="n">
-        <v>0.588</v>
+        <v>0.6388</v>
       </c>
       <c r="BC9" s="2" t="n">
-        <v>0.5678</v>
+        <v>0.6157</v>
       </c>
       <c r="BD9" s="2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="BE9" s="2" t="n">
-        <v>0.5468</v>
+        <v>0.5986</v>
       </c>
       <c r="BF9" s="2" t="n">
-        <v>0.5515</v>
+        <v>0.6095</v>
       </c>
       <c r="BG9" s="2" t="n">
-        <v>0.5336</v>
+        <v>0.5884</v>
       </c>
       <c r="BH9" s="2" t="n">
-        <v>0.8786</v>
+        <v>0.9043</v>
       </c>
     </row>
     <row r="10">
@@ -2256,181 +2256,181 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.7581</v>
+        <v>0.7936</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7557</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.3875</v>
+        <v>0.4375</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8579</v>
+        <v>0.8767</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.3173</v>
+        <v>0.3345</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.959</v>
+        <v>0.957</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.8865</v>
+        <v>0.9107</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>51.828</v>
+        <v>55.263</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>36280.36</v>
+        <v>40920.083</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>34801.238</v>
+        <v>39146.879</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>29855.567</v>
+        <v>34320.843</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>583.4</v>
+        <v>589.5</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>739.353</v>
+        <v>757.544</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>888.8200000000001</v>
+        <v>934.693</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>1.2022</v>
+        <v>1.2338</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>428.167</v>
+        <v>428.925</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>4.385</v>
+        <v>4.406</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.945</v>
+        <v>0.9564</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.3046</v>
+        <v>0.3033</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.3892</v>
+        <v>0.4341</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1082</v>
+        <v>0.0922</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0.3565</v>
+        <v>0.4007</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.101</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.8945</v>
+        <v>0.9194</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.9487</v>
+        <v>0.9606</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.3061</v>
+        <v>0.3025</v>
       </c>
       <c r="AG10" s="2" t="n">
-        <v>51.268</v>
+        <v>54.408</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>0.3817</v>
+        <v>0.4228</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>129.1</v>
+        <v>147.9</v>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>8.462</v>
+        <v>8.667</v>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>5.022</v>
+        <v>5.152</v>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>0.9468</v>
+        <v>0.9585</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>0.3624</v>
+        <v>0.4127</v>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.6391</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="AO10" s="2" t="n">
-        <v>29.559</v>
+        <v>32.346</v>
       </c>
       <c r="AP10" s="2" t="n">
-        <v>31.177</v>
+        <v>33.817</v>
       </c>
       <c r="AQ10" s="2" t="n">
-        <v>49.666</v>
+        <v>53.371</v>
       </c>
       <c r="AR10" s="2" t="n">
-        <v>18.489</v>
+        <v>19.554</v>
       </c>
       <c r="AS10" s="2" t="n">
-        <v>21.71</v>
+        <v>22.062</v>
       </c>
       <c r="AT10" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="AU10" s="2" t="n">
-        <v>122.6</v>
+        <v>144.3</v>
       </c>
       <c r="AV10" s="2" t="n">
-        <v>166.662</v>
+        <v>186.196</v>
       </c>
       <c r="AW10" s="2" t="n">
-        <v>248.446</v>
+        <v>269.789</v>
       </c>
       <c r="AX10" s="2" t="n">
-        <v>253.094</v>
+        <v>274.935</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>160.781</v>
+        <v>179.867</v>
       </c>
       <c r="AZ10" s="2" t="n">
-        <v>583.4</v>
+        <v>589.5</v>
       </c>
       <c r="BA10" s="2" t="n">
-        <v>536.7</v>
+        <v>535.4</v>
       </c>
       <c r="BB10" s="2" t="n">
-        <v>0.5671</v>
+        <v>0.6116</v>
       </c>
       <c r="BC10" s="2" t="n">
-        <v>0.5484</v>
+        <v>0.5904</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.5485</v>
+        <v>0.5966</v>
       </c>
       <c r="BE10" s="2" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5759</v>
       </c>
       <c r="BF10" s="2" t="n">
-        <v>0.536</v>
+        <v>0.5867</v>
       </c>
       <c r="BG10" s="2" t="n">
-        <v>0.519</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="BH10" s="2" t="n">
-        <v>0.893</v>
+        <v>0.9159</v>
       </c>
     </row>
     <row r="11">
@@ -2438,181 +2438,181 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8298</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.763</v>
+        <v>0.7978</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.7216</v>
+        <v>0.7644</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>338.15</v>
+        <v>349.76</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.3817</v>
+        <v>0.4228</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>129.1</v>
+        <v>147.9</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.8549</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.3192</v>
+        <v>0.3415</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.955</v>
+        <v>0.952</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.8995</v>
+        <v>0.9211</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>51.126</v>
+        <v>54.361</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>36503.665</v>
+        <v>41773.536</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>34875.04</v>
+        <v>39789.293</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>29815.46</v>
+        <v>34714.229</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>616.6</v>
+        <v>627.3</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>888.8200000000001</v>
+        <v>934.693</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>1057.365</v>
+        <v>1140.911</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>1.1896</v>
+        <v>1.2206</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>440.712</v>
+        <v>442.978</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>4.991</v>
+        <v>5.134</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9614</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>0.3077</v>
+        <v>0.3031</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0.3762</v>
+        <v>0.4107</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>0.0965</v>
+        <v>0.0819</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>0.3437</v>
+        <v>0.3782</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>0.0911</v>
+        <v>0.0752</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>0.9054</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>0.9539</v>
+        <v>0.9641</v>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>338.15</v>
+        <v>347.12</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>0.3086</v>
+        <v>0.3017</v>
       </c>
       <c r="AG11" s="2" t="n">
-        <v>50.623</v>
+        <v>53.518</v>
       </c>
       <c r="AH11" s="2" t="n">
-        <v>0.3761</v>
+        <v>0.4084</v>
       </c>
       <c r="AI11" s="2" t="n">
-        <v>127.2</v>
+        <v>141.8</v>
       </c>
       <c r="AJ11" s="2" t="n">
-        <v>8.769</v>
+        <v>9</v>
       </c>
       <c r="AK11" s="2" t="n">
-        <v>5.675</v>
+        <v>5.954</v>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>0.9525</v>
+        <v>0.9628</v>
       </c>
       <c r="AM11" s="2" t="n">
-        <v>0.3558</v>
+        <v>0.397</v>
       </c>
       <c r="AN11" s="2" t="n">
-        <v>0.6424</v>
+        <v>0.6573</v>
       </c>
       <c r="AO11" s="2" t="n">
-        <v>28.977</v>
+        <v>31.131</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>30.68</v>
+        <v>32.709</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>48.927</v>
+        <v>52.43</v>
       </c>
       <c r="AR11" s="2" t="n">
-        <v>18.247</v>
+        <v>19.721</v>
       </c>
       <c r="AS11" s="2" t="n">
-        <v>21.646</v>
+        <v>22.386</v>
       </c>
       <c r="AT11" s="2" t="n">
-        <v>338.15</v>
+        <v>348.44</v>
       </c>
       <c r="AU11" s="2" t="n">
-        <v>120.3</v>
+        <v>138.9</v>
       </c>
       <c r="AV11" s="2" t="n">
-        <v>165.788</v>
+        <v>181.941</v>
       </c>
       <c r="AW11" s="2" t="n">
-        <v>248.32</v>
+        <v>268.595</v>
       </c>
       <c r="AX11" s="2" t="n">
-        <v>252.961</v>
+        <v>273.635</v>
       </c>
       <c r="AY11" s="2" t="n">
-        <v>159.577</v>
+        <v>175.2</v>
       </c>
       <c r="AZ11" s="2" t="n">
-        <v>616.6</v>
+        <v>627.3</v>
       </c>
       <c r="BA11" s="2" t="n">
-        <v>570.3</v>
+        <v>573.8</v>
       </c>
       <c r="BB11" s="2" t="n">
-        <v>0.5484</v>
+        <v>0.5834</v>
       </c>
       <c r="BC11" s="2" t="n">
-        <v>0.5309</v>
+        <v>0.5649</v>
       </c>
       <c r="BD11" s="2" t="n">
-        <v>0.5326</v>
+        <v>0.5745</v>
       </c>
       <c r="BE11" s="2" t="n">
-        <v>0.5158</v>
+        <v>0.5554</v>
       </c>
       <c r="BF11" s="2" t="n">
-        <v>0.5216</v>
+        <v>0.5619</v>
       </c>
       <c r="BG11" s="2" t="n">
-        <v>0.5054</v>
+        <v>0.5445</v>
       </c>
       <c r="BH11" s="2" t="n">
-        <v>0.9048</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="12">
@@ -2620,181 +2620,181 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8235</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.7671</v>
+        <v>0.7945</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.7302</v>
+        <v>0.7644</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>338.15</v>
+        <v>347.12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.3761</v>
+        <v>0.4084</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>127.2</v>
+        <v>141.8</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.8519</v>
+        <v>0.8673</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.3211</v>
+        <v>0.3478</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.952</v>
+        <v>0.948</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.9102</v>
+        <v>0.9282</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>50.485</v>
+        <v>53.511</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>36714.101</v>
+        <v>42550.97</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>34934.879</v>
+        <v>40352.503</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>29760.379</v>
+        <v>34996.946</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>649.6</v>
+        <v>665.4</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>1057.365</v>
+        <v>1140.911</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>1246.087</v>
+        <v>1378.51</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>1.1785</v>
+        <v>1.2083</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>452.82</v>
+        <v>456.671</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>5.64</v>
+        <v>5.938</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.9562</v>
+        <v>0.9647</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.3102</v>
+        <v>0.3021</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>0.364</v>
+        <v>0.3862</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.0867</v>
+        <v>0.0738</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>0.3317</v>
+        <v>0.3499</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>0.0827</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>0.9146</v>
+        <v>0.9327</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9669</v>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>338.15</v>
+        <v>344.88</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>0.3107</v>
+        <v>0.2904</v>
       </c>
       <c r="AG12" s="2" t="n">
-        <v>50.025</v>
+        <v>53.64</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>0.3706</v>
+        <v>0.3945</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>125.3</v>
+        <v>136</v>
       </c>
       <c r="AJ12" s="2" t="n">
-        <v>9.077</v>
+        <v>9.333</v>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>6.369</v>
+        <v>6.842</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9658</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>0.3492</v>
+        <v>0.3816</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>0.6453</v>
+        <v>0.6619</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>28.423</v>
+        <v>29.962</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>30.207</v>
+        <v>31.649</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>48.231</v>
+        <v>51.46</v>
       </c>
       <c r="AR12" s="2" t="n">
-        <v>18.023</v>
+        <v>19.81</v>
       </c>
       <c r="AS12" s="2" t="n">
-        <v>21.603</v>
+        <v>23.679</v>
       </c>
       <c r="AT12" s="2" t="n">
-        <v>338.15</v>
+        <v>346</v>
       </c>
       <c r="AU12" s="2" t="n">
-        <v>118.1</v>
+        <v>132.4</v>
       </c>
       <c r="AV12" s="2" t="n">
-        <v>164.845</v>
+        <v>176.347</v>
       </c>
       <c r="AW12" s="2" t="n">
-        <v>248.11</v>
+        <v>265.198</v>
       </c>
       <c r="AX12" s="2" t="n">
-        <v>252.761</v>
+        <v>270.201</v>
       </c>
       <c r="AY12" s="2" t="n">
-        <v>158.338</v>
+        <v>169.331</v>
       </c>
       <c r="AZ12" s="2" t="n">
-        <v>649.6</v>
+        <v>665.4</v>
       </c>
       <c r="BA12" s="2" t="n">
-        <v>603.7</v>
+        <v>612.7</v>
       </c>
       <c r="BB12" s="2" t="n">
-        <v>0.5316</v>
+        <v>0.5594</v>
       </c>
       <c r="BC12" s="2" t="n">
-        <v>0.5151</v>
+        <v>0.5421</v>
       </c>
       <c r="BD12" s="2" t="n">
-        <v>0.5179</v>
+        <v>0.5498</v>
       </c>
       <c r="BE12" s="2" t="n">
-        <v>0.502</v>
+        <v>0.5319</v>
       </c>
       <c r="BF12" s="2" t="n">
-        <v>0.5082</v>
+        <v>0.5404</v>
       </c>
       <c r="BG12" s="2" t="n">
-        <v>0.4928</v>
+        <v>0.524</v>
       </c>
       <c r="BH12" s="2" t="n">
-        <v>0.9147</v>
+        <v>0.9312</v>
       </c>
     </row>
     <row r="13">
@@ -2802,181 +2802,181 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.8023</v>
+        <v>0.8182</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.7705</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7644</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>338.15</v>
+        <v>344.88</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.3706</v>
+        <v>0.3945</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>125.3</v>
+        <v>136</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8488</v>
+        <v>0.8509</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.3228</v>
+        <v>0.3359</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.948</v>
+        <v>0.944</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.9192</v>
+        <v>0.9342</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>49.891</v>
+        <v>53.594</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>36912.932</v>
+        <v>41096.268</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>34982.102</v>
+        <v>38801.726</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>29691.639</v>
+        <v>33017.704</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>682.4</v>
+        <v>701.7</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>1246.087</v>
+        <v>1378.51</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>1456.061</v>
+        <v>1631.954</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>1.1685</v>
+        <v>1.1839</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>464.52</v>
+        <v>470.006</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>6.33</v>
+        <v>6.822</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.9604</v>
+        <v>0.9677</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.3122</v>
+        <v>0.2909</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>0.3527</v>
+        <v>0.3596</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.0784</v>
+        <v>0.0669</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>0.3159</v>
+        <v>0.321</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0635</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9372</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>0.9618</v>
+        <v>0.9691</v>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>335.8</v>
+        <v>343.11</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>0.3014</v>
+        <v>0.2695</v>
       </c>
       <c r="AG13" s="2" t="n">
-        <v>50.459</v>
+        <v>54.721</v>
       </c>
       <c r="AH13" s="2" t="n">
-        <v>0.3652</v>
+        <v>0.3808</v>
       </c>
       <c r="AI13" s="2" t="n">
-        <v>122.6</v>
+        <v>130.7</v>
       </c>
       <c r="AJ13" s="2" t="n">
-        <v>9.385</v>
+        <v>9.667</v>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>7.115</v>
+        <v>7.745</v>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>0.9611</v>
+        <v>0.9684</v>
       </c>
       <c r="AM13" s="2" t="n">
-        <v>0.3428</v>
+        <v>0.3665</v>
       </c>
       <c r="AN13" s="2" t="n">
-        <v>0.6478</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>27.888</v>
+        <v>29.888</v>
       </c>
       <c r="AP13" s="2" t="n">
-        <v>29.755</v>
+        <v>30.238</v>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>47.582</v>
+        <v>47.926</v>
       </c>
       <c r="AR13" s="2" t="n">
-        <v>17.826</v>
+        <v>17.689</v>
       </c>
       <c r="AS13" s="2" t="n">
-        <v>22.57</v>
+        <v>24.833</v>
       </c>
       <c r="AT13" s="2" t="n">
-        <v>336.97</v>
+        <v>343.99</v>
       </c>
       <c r="AU13" s="2" t="n">
-        <v>115.9</v>
+        <v>126.4</v>
       </c>
       <c r="AV13" s="2" t="n">
-        <v>163.853</v>
+        <v>169.037</v>
       </c>
       <c r="AW13" s="2" t="n">
-        <v>247.853</v>
+        <v>253.616</v>
       </c>
       <c r="AX13" s="2" t="n">
-        <v>252.509</v>
+        <v>270.155</v>
       </c>
       <c r="AY13" s="2" t="n">
-        <v>157.041</v>
+        <v>170.259</v>
       </c>
       <c r="AZ13" s="2" t="n">
-        <v>682.4</v>
+        <v>701.7</v>
       </c>
       <c r="BA13" s="2" t="n">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="BB13" s="2" t="n">
-        <v>0.5131</v>
+        <v>0.5421</v>
       </c>
       <c r="BC13" s="2" t="n">
-        <v>0.4983</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="BD13" s="2" t="n">
-        <v>0.5044</v>
+        <v>0.5337</v>
       </c>
       <c r="BE13" s="2" t="n">
-        <v>0.4893</v>
+        <v>0.4943</v>
       </c>
       <c r="BF13" s="2" t="n">
-        <v>0.4924</v>
+        <v>0.5289</v>
       </c>
       <c r="BG13" s="2" t="n">
-        <v>0.4785</v>
+        <v>0.4891</v>
       </c>
       <c r="BH13" s="2" t="n">
-        <v>0.9224</v>
+        <v>0.9366</v>
       </c>
     </row>
     <row r="14">
@@ -2984,363 +2984,181 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.7967</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7896</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7644</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>335.8</v>
+        <v>343.11</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.3652</v>
+        <v>0.3808</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>122.6</v>
+        <v>130.7</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8354</v>
+        <v>0.8331</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.3082</v>
+        <v>0.323</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.944</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.9256</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>50.364</v>
+        <v>54.665</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>35246.122</v>
+        <v>39513.494</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>33266.917</v>
+        <v>37142.685</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>27792.261</v>
+        <v>30943.821</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>713.4</v>
+        <v>736.1</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>1456.061</v>
+        <v>1631.954</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>1673.342</v>
+        <v>1896.809</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>1.1492</v>
+        <v>1.1623</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>475.843</v>
+        <v>482.35</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>7.078</v>
+        <v>7.721</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.9635</v>
+        <v>0.97</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.3025</v>
+        <v>0.27</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>0.3347</v>
+        <v>0.3321</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0615</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>0.2949</v>
+        <v>0.2444</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9413</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>0.9641</v>
+        <v>0.9711</v>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>333.93</v>
+        <v>342.26</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>0.2817</v>
+        <v>0.27</v>
       </c>
       <c r="AG14" s="2" t="n">
-        <v>51.96</v>
+        <v>90</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>0.36</v>
+        <v>0.3517</v>
       </c>
       <c r="AI14" s="2" t="n">
-        <v>120.2</v>
+        <v>120.7</v>
       </c>
       <c r="AJ14" s="2" t="n">
-        <v>9.692</v>
+        <v>10</v>
       </c>
       <c r="AK14" s="2" t="n">
-        <v>7.865</v>
+        <v>8.741</v>
       </c>
       <c r="AL14" s="2" t="n">
-        <v>0.9638</v>
+        <v>0.9705</v>
       </c>
       <c r="AM14" s="2" t="n">
-        <v>0.3364</v>
+        <v>0.3517</v>
       </c>
       <c r="AN14" s="2" t="n">
-        <v>0.6223</v>
+        <v>0.6026</v>
       </c>
       <c r="AO14" s="2" t="n">
-        <v>28.395</v>
+        <v>30.267</v>
       </c>
       <c r="AP14" s="2" t="n">
-        <v>28.924</v>
+        <v>28.549</v>
       </c>
       <c r="AQ14" s="2" t="n">
-        <v>44.56</v>
+        <v>43.709</v>
       </c>
       <c r="AR14" s="2" t="n">
-        <v>15.636</v>
+        <v>15.16</v>
       </c>
       <c r="AS14" s="2" t="n">
-        <v>23.565</v>
+        <v>59.733</v>
       </c>
       <c r="AT14" s="2" t="n">
-        <v>334.87</v>
+        <v>342.68</v>
       </c>
       <c r="AU14" s="2" t="n">
-        <v>113</v>
+        <v>120.7</v>
       </c>
       <c r="AV14" s="2" t="n">
-        <v>159.261</v>
+        <v>160.175</v>
       </c>
       <c r="AW14" s="2" t="n">
-        <v>237.528</v>
+        <v>239.404</v>
       </c>
       <c r="AX14" s="2" t="n">
-        <v>253.591</v>
+        <v>273.415</v>
       </c>
       <c r="AY14" s="2" t="n">
-        <v>160.985</v>
+        <v>174.629</v>
       </c>
       <c r="AZ14" s="2" t="n">
-        <v>713.4</v>
+        <v>736.1</v>
       </c>
       <c r="BA14" s="2" t="n">
-        <v>670.6</v>
+        <v>689.8</v>
       </c>
       <c r="BB14" s="2" t="n">
-        <v>0.5016</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="BC14" s="2" t="n">
-        <v>0.467</v>
+        <v>0.4648</v>
       </c>
       <c r="BD14" s="2" t="n">
-        <v>0.4943</v>
+        <v>0.5259</v>
       </c>
       <c r="BE14" s="2" t="n">
-        <v>0.4579</v>
+        <v>0.4546</v>
       </c>
       <c r="BF14" s="2" t="n">
-        <v>0.4873</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="BG14" s="2" t="n">
-        <v>0.45</v>
+        <v>0.4518</v>
       </c>
       <c r="BH14" s="2" t="n">
-        <v>0.9282</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0.7653</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0.7374000000000001</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>333.93</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0.8213</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0.2934</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0.9308</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>51.845</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>33551.722</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>31538.619</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>25901.518</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>742.6</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>1673.342</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>1894.737</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>1.1323</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>486.271</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>7.825</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>0.2828</v>
-      </c>
-      <c r="Y15" s="2" t="n">
-        <v>0.3144</v>
-      </c>
-      <c r="Z15" s="2" t="n">
-        <v>0.0659</v>
-      </c>
-      <c r="AA15" s="2" t="n">
-        <v>0.2223</v>
-      </c>
-      <c r="AB15" s="2" t="n">
-        <v>0.0649</v>
-      </c>
-      <c r="AC15" s="2" t="n">
-        <v>0.9317</v>
-      </c>
-      <c r="AD15" s="2" t="n">
-        <v>0.9665</v>
-      </c>
-      <c r="AE15" s="2" t="n">
-        <v>333.61</v>
-      </c>
-      <c r="AF15" s="2" t="n">
-        <v>0.2828</v>
-      </c>
-      <c r="AG15" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AH15" s="2" t="n">
-        <v>0.3301</v>
-      </c>
-      <c r="AI15" s="2" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="AJ15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK15" s="2" t="n">
-        <v>8.694000000000001</v>
-      </c>
-      <c r="AL15" s="2" t="n">
-        <v>0.9661999999999999</v>
-      </c>
-      <c r="AM15" s="2" t="n">
-        <v>0.3301</v>
-      </c>
-      <c r="AN15" s="2" t="n">
-        <v>0.5864</v>
-      </c>
-      <c r="AO15" s="2" t="n">
-        <v>29.371</v>
-      </c>
-      <c r="AP15" s="2" t="n">
-        <v>27.787</v>
-      </c>
-      <c r="AQ15" s="2" t="n">
-        <v>40.992</v>
-      </c>
-      <c r="AR15" s="2" t="n">
-        <v>13.205</v>
-      </c>
-      <c r="AS15" s="2" t="n">
-        <v>60.629</v>
-      </c>
-      <c r="AT15" s="2" t="n">
-        <v>333.77</v>
-      </c>
-      <c r="AU15" s="2" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="AV15" s="2" t="n">
-        <v>152.881</v>
-      </c>
-      <c r="AW15" s="2" t="n">
-        <v>224.72</v>
-      </c>
-      <c r="AX15" s="2" t="n">
-        <v>257.874</v>
-      </c>
-      <c r="AY15" s="2" t="n">
-        <v>168.024</v>
-      </c>
-      <c r="AZ15" s="2" t="n">
-        <v>742.6</v>
-      </c>
-      <c r="BA15" s="2" t="n">
-        <v>702.6</v>
-      </c>
-      <c r="BB15" s="2" t="n">
-        <v>0.4975</v>
-      </c>
-      <c r="BC15" s="2" t="n">
-        <v>0.4334</v>
-      </c>
-      <c r="BD15" s="2" t="n">
-        <v>0.4917</v>
-      </c>
-      <c r="BE15" s="2" t="n">
-        <v>0.4239</v>
-      </c>
-      <c r="BF15" s="2" t="n">
-        <v>0.4899</v>
-      </c>
-      <c r="BG15" s="2" t="n">
-        <v>0.4188</v>
-      </c>
-      <c r="BH15" s="2" t="n">
-        <v>0.9313</v>
+        <v>0.9402</v>
       </c>
     </row>
   </sheetData>
